--- a/STM32F407ZGT6_PinMux.xlsx
+++ b/STM32F407ZGT6_PinMux.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yourfather\Desktop\stm32f407\F407\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7D1B33-55C1-440D-A684-55AE6938538A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A2AD21-987F-41DB-A743-45DDB713FE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{E862E505-DAE5-417D-B231-6254909BD249}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{E862E505-DAE5-417D-B231-6254909BD249}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="269">
   <si>
     <t>STM32F407ZGT6</t>
   </si>
@@ -843,30 +843,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A_Phase</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A_Phase_N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B_Phase</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B_Phase_N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C_Phase_N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C_Phase</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ADC0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -908,10 +884,6 @@
   </si>
   <si>
     <t>LCD CS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BKIN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -988,7 +960,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -999,6 +971,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1780,7 +1755,7 @@
         <v>64</v>
       </c>
       <c r="C36" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D36" t="s">
         <v>65</v>
@@ -1794,7 +1769,7 @@
         <v>66</v>
       </c>
       <c r="C37" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D37" t="s">
         <v>67</v>
@@ -1808,7 +1783,7 @@
         <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D38" t="s">
         <v>69</v>
@@ -1822,7 +1797,7 @@
         <v>70</v>
       </c>
       <c r="C39" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D39" t="s">
         <v>71</v>
@@ -1852,7 +1827,7 @@
         <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>73</v>
@@ -1866,7 +1841,7 @@
         <v>74</v>
       </c>
       <c r="C43" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D43" t="s">
         <v>75</v>
@@ -1935,7 +1910,7 @@
       <c r="B48" t="s">
         <v>84</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D48" t="s">
@@ -1949,7 +1924,7 @@
       <c r="B49" t="s">
         <v>86</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="4" t="s">
         <v>86</v>
       </c>
       <c r="D49" t="s">
@@ -2099,11 +2074,11 @@
       <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>258</v>
+      <c r="C61" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="D61" t="s">
         <v>107</v>
@@ -2113,11 +2088,11 @@
       <c r="A62">
         <v>60</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>257</v>
+      <c r="C62" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="D62" t="s">
         <v>109</v>
@@ -2143,11 +2118,11 @@
       <c r="A65">
         <v>63</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>260</v>
+      <c r="C65" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="D65" t="s">
         <v>111</v>
@@ -2157,11 +2132,11 @@
       <c r="A66">
         <v>64</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>259</v>
+      <c r="C66" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="D66" t="s">
         <v>113</v>
@@ -2171,11 +2146,11 @@
       <c r="A67">
         <v>65</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>261</v>
+      <c r="C67" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="D67" t="s">
         <v>115</v>
@@ -2185,11 +2160,11 @@
       <c r="A68">
         <v>66</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>262</v>
+      <c r="C68" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="D68" t="s">
         <v>117</v>
@@ -2213,11 +2188,11 @@
       <c r="A70">
         <v>68</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>275</v>
+      <c r="C70" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="D70" t="s">
         <v>121</v>
@@ -2567,6 +2542,7 @@
       <c r="B97" t="s">
         <v>36</v>
       </c>
+      <c r="D97" s="4"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98">
@@ -2575,10 +2551,10 @@
       <c r="B98" t="s">
         <v>166</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="4" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2589,7 +2565,7 @@
       <c r="B99" t="s">
         <v>168</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D99" t="s">
@@ -2603,7 +2579,7 @@
       <c r="B100" t="s">
         <v>170</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="4" t="s">
         <v>170</v>
       </c>
       <c r="D100" t="s">
@@ -2617,7 +2593,7 @@
       <c r="B101" t="s">
         <v>172</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="4" t="s">
         <v>172</v>
       </c>
       <c r="D101" t="s">
@@ -2631,7 +2607,7 @@
       <c r="B102" t="s">
         <v>174</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="4" t="s">
         <v>174</v>
       </c>
       <c r="D102" t="s">
@@ -2804,7 +2780,7 @@
         <v>196</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D116" t="s">
         <v>197</v>
@@ -2818,7 +2794,7 @@
         <v>198</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D117" t="s">
         <v>199</v>
@@ -2832,7 +2808,7 @@
         <v>200</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D118" t="s">
         <v>201</v>
@@ -2846,7 +2822,7 @@
         <v>202</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
         <v>203</v>
@@ -2860,7 +2836,7 @@
         <v>204</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D120" t="s">
         <v>205</v>
@@ -2874,7 +2850,7 @@
         <v>206</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D121" t="s">
         <v>207</v>

--- a/STM32F407ZGT6_PinMux.xlsx
+++ b/STM32F407ZGT6_PinMux.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yourfather\Desktop\stm32f407\F407\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yourfather\Desktop\stm32f407\github\20250606\study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A2AD21-987F-41DB-A743-45DDB713FE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{09F8F41B-3416-4EB0-85A3-8B6579177378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{E862E505-DAE5-417D-B231-6254909BD249}"/>
   </bookViews>
@@ -264,9 +264,6 @@
     <t>PA7</t>
   </si>
   <si>
-    <t>PA7/SPI1_MOSI/ TIM8_CH1N /TIM14_CH1/TIM3_CH2/ETH_MII_RX_DV /TIM1_CH1N /ETH_RMII_CRS_DV/EVENTOUT/ADC12_IN7</t>
-  </si>
-  <si>
     <t>PC4</t>
   </si>
   <si>
@@ -426,15 +423,9 @@
     <t>PB14</t>
   </si>
   <si>
-    <t>SPI2_MISO/ TIM1_CH2N /TIM12_CH1 /OTG_HS_DM/USART3_RTS /TIM8_CH2N/I2S2ext_SD/EVENTOUT</t>
-  </si>
-  <si>
     <t>PB15</t>
   </si>
   <si>
-    <t>SPI2_MOSI / I2S2_SD/TIM1_CH3N / TIM8_CH3N/ TIM12_CH2 /OTG_HS_DP/ EVENTOUT/RTC_REFIN</t>
-  </si>
-  <si>
     <t>PD8</t>
   </si>
   <si>
@@ -528,19 +519,10 @@
     <t>PC6</t>
   </si>
   <si>
-    <t>I2S2_MCK /TIM8_CH1/SDIO_D6 /USART6_TX /DCMI_D0/TIM3_CH1/EVENTOUT</t>
-  </si>
-  <si>
     <t>PC7</t>
   </si>
   <si>
-    <t>I2S3_MCK /TIM8_CH2/SDIO_D7 /USART6_RX /DCMI_D1/TIM3_CH2/EVENTOUT</t>
-  </si>
-  <si>
     <t>PC8</t>
-  </si>
-  <si>
-    <t>TIM8_CH3/SDIO_D0/TIM3_CH3/ USART6_CK /DCMI_D2/ EVENTOUT</t>
   </si>
   <si>
     <t>PC9</t>
@@ -886,12 +868,177 @@
     <t>LCD CS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t>I2S2_MCK /</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TIM8_CH1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/SDIO_D6 /USART6_TX /DCMI_D0/TIM3_CH1/EVENTOUT</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I2S3_MCK /</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TIM8_CH2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/SDIO_D7 /USART6_RX /DCMI_D1/TIM3_CH2/EVENTOUT</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TIM8_CH3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/SDIO_D0/TIM3_CH3/ USART6_CK /DCMI_D2/ EVENTOUT</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SPI2_MOSI / I2S2_SD/TIM1_CH3N / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TIM8_CH3N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ TIM12_CH2 /OTG_HS_DP/ EVENTOUT/RTC_REFIN</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SPI2_MISO/ TIM1_CH2N /TIM12_CH1 /OTG_HS_DM/USART3_RTS /</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TIM8_CH2N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/I2S2ext_SD/EVENTOUT</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PA7/SPI1_MOSI/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TIM8_CH1N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> /TIM14_CH1/TIM3_CH2/ETH_MII_RX_DV /TIM1_CH1N /ETH_RMII_CRS_DV/EVENTOUT/ADC12_IN7</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -931,8 +1078,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -942,6 +1097,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -973,7 +1134,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1600,7 +1761,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D23" t="s">
         <v>44</v>
@@ -1614,7 +1775,7 @@
         <v>45</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D24" t="s">
         <v>46</v>
@@ -1755,7 +1916,7 @@
         <v>64</v>
       </c>
       <c r="C36" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D36" t="s">
         <v>65</v>
@@ -1769,7 +1930,7 @@
         <v>66</v>
       </c>
       <c r="C37" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D37" t="s">
         <v>67</v>
@@ -1783,7 +1944,7 @@
         <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D38" t="s">
         <v>69</v>
@@ -1797,7 +1958,7 @@
         <v>70</v>
       </c>
       <c r="C39" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D39" t="s">
         <v>71</v>
@@ -1827,7 +1988,7 @@
         <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D42" t="s">
         <v>73</v>
@@ -1841,7 +2002,7 @@
         <v>74</v>
       </c>
       <c r="C43" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D43" t="s">
         <v>75</v>
@@ -1868,11 +2029,11 @@
       <c r="B45" t="s">
         <v>78</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="4" t="s">
         <v>78</v>
       </c>
       <c r="D45" t="s">
-        <v>79</v>
+        <v>268</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1880,13 +2041,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" t="s">
         <v>80</v>
-      </c>
-      <c r="C46" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1894,13 +2055,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" t="s">
         <v>82</v>
-      </c>
-      <c r="C47" t="s">
-        <v>82</v>
-      </c>
-      <c r="D47" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1908,13 +2069,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
+        <v>83</v>
+      </c>
+      <c r="C48" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" t="s">
         <v>84</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D48" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1922,13 +2083,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49" t="s">
+        <v>85</v>
+      </c>
+      <c r="D49" t="s">
         <v>86</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D49" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1936,10 +2097,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" t="s">
         <v>88</v>
-      </c>
-      <c r="C50" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1947,13 +2108,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51" t="s">
         <v>90</v>
-      </c>
-      <c r="C51" t="s">
-        <v>90</v>
-      </c>
-      <c r="D51" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1961,13 +2122,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
+        <v>91</v>
+      </c>
+      <c r="C52" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" t="s">
         <v>92</v>
-      </c>
-      <c r="C52" t="s">
-        <v>92</v>
-      </c>
-      <c r="D52" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1991,13 +2152,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
+        <v>93</v>
+      </c>
+      <c r="C55" t="s">
+        <v>93</v>
+      </c>
+      <c r="D55" t="s">
         <v>94</v>
-      </c>
-      <c r="C55" t="s">
-        <v>94</v>
-      </c>
-      <c r="D55" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -2005,13 +2166,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
+        <v>95</v>
+      </c>
+      <c r="C56" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56" t="s">
         <v>96</v>
-      </c>
-      <c r="C56" t="s">
-        <v>96</v>
-      </c>
-      <c r="D56" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2019,13 +2180,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" t="s">
+        <v>97</v>
+      </c>
+      <c r="D57" t="s">
         <v>98</v>
-      </c>
-      <c r="C57" t="s">
-        <v>98</v>
-      </c>
-      <c r="D57" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -2033,13 +2194,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" t="s">
+        <v>99</v>
+      </c>
+      <c r="D58" t="s">
         <v>100</v>
-      </c>
-      <c r="C58" t="s">
-        <v>100</v>
-      </c>
-      <c r="D58" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -2047,13 +2208,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
+        <v>101</v>
+      </c>
+      <c r="C59" t="s">
+        <v>101</v>
+      </c>
+      <c r="D59" t="s">
         <v>102</v>
-      </c>
-      <c r="C59" t="s">
-        <v>102</v>
-      </c>
-      <c r="D59" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2061,41 +2222,41 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" t="s">
+        <v>103</v>
+      </c>
+      <c r="D60" t="s">
         <v>104</v>
-      </c>
-      <c r="C60" t="s">
-        <v>104</v>
-      </c>
-      <c r="D60" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" t="s">
+        <v>105</v>
+      </c>
+      <c r="C61" t="s">
+        <v>105</v>
+      </c>
+      <c r="D61" t="s">
         <v>106</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D61" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>60</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" t="s">
+        <v>107</v>
+      </c>
+      <c r="C62" t="s">
+        <v>107</v>
+      </c>
+      <c r="D62" t="s">
         <v>108</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D62" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2118,56 +2279,56 @@
       <c r="A65">
         <v>63</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" t="s">
+        <v>109</v>
+      </c>
+      <c r="C65" t="s">
+        <v>109</v>
+      </c>
+      <c r="D65" t="s">
         <v>110</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D65" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>64</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" t="s">
+        <v>111</v>
+      </c>
+      <c r="C66" t="s">
+        <v>111</v>
+      </c>
+      <c r="D66" t="s">
         <v>112</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D66" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>65</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" t="s">
+        <v>113</v>
+      </c>
+      <c r="C67" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" t="s">
         <v>114</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D67" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>66</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" t="s">
+        <v>115</v>
+      </c>
+      <c r="C68" t="s">
+        <v>115</v>
+      </c>
+      <c r="D68" t="s">
         <v>116</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D68" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -2175,27 +2336,27 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
+        <v>117</v>
+      </c>
+      <c r="C69" t="s">
+        <v>117</v>
+      </c>
+      <c r="D69" t="s">
         <v>118</v>
-      </c>
-      <c r="C69" t="s">
-        <v>118</v>
-      </c>
-      <c r="D69" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>68</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" t="s">
+        <v>119</v>
+      </c>
+      <c r="C70" t="s">
+        <v>119</v>
+      </c>
+      <c r="D70" t="s">
         <v>120</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D70" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -2203,13 +2364,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
+        <v>121</v>
+      </c>
+      <c r="C71" t="s">
+        <v>121</v>
+      </c>
+      <c r="D71" t="s">
         <v>122</v>
-      </c>
-      <c r="C71" t="s">
-        <v>122</v>
-      </c>
-      <c r="D71" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -2217,13 +2378,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
+        <v>123</v>
+      </c>
+      <c r="C72" t="s">
+        <v>123</v>
+      </c>
+      <c r="D72" t="s">
         <v>124</v>
-      </c>
-      <c r="C72" t="s">
-        <v>124</v>
-      </c>
-      <c r="D72" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -2231,10 +2392,10 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
+        <v>125</v>
+      </c>
+      <c r="D73" t="s">
         <v>126</v>
-      </c>
-      <c r="D73" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -2250,13 +2411,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
+        <v>127</v>
+      </c>
+      <c r="C75" t="s">
+        <v>127</v>
+      </c>
+      <c r="D75" t="s">
         <v>128</v>
-      </c>
-      <c r="C75" t="s">
-        <v>128</v>
-      </c>
-      <c r="D75" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -2264,13 +2425,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
+        <v>129</v>
+      </c>
+      <c r="C76" t="s">
+        <v>129</v>
+      </c>
+      <c r="D76" t="s">
         <v>130</v>
-      </c>
-      <c r="C76" t="s">
-        <v>130</v>
-      </c>
-      <c r="D76" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -2278,13 +2439,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>132</v>
-      </c>
-      <c r="C77" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="D77" t="s">
-        <v>133</v>
+        <v>267</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -2292,13 +2453,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>134</v>
-      </c>
-      <c r="C78" t="s">
-        <v>134</v>
+        <v>132</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="D78" t="s">
-        <v>135</v>
+        <v>266</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -2306,13 +2467,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C79" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D79" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -2320,13 +2481,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C80" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D80" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -2334,13 +2495,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C81" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D81" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2348,13 +2509,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C82" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D82" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -2362,13 +2523,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C83" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D83" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -2376,13 +2537,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C84" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D84" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -2406,13 +2567,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C87" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D87" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -2420,13 +2581,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C88" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D88" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -2434,13 +2595,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C89" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D89" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -2448,13 +2609,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C90" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D90" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -2462,13 +2623,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C91" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D91" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -2476,13 +2637,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C92" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D92" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -2490,13 +2651,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C93" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D93" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -2504,13 +2665,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C94" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D94" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -2518,13 +2679,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C95" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D95" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -2542,20 +2703,19 @@
       <c r="B97" t="s">
         <v>36</v>
       </c>
-      <c r="D97" s="4"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>167</v>
+        <v>163</v>
+      </c>
+      <c r="D98" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -2563,13 +2723,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D99" t="s">
-        <v>169</v>
+        <v>264</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -2577,13 +2737,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D100" t="s">
-        <v>171</v>
+        <v>165</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -2591,13 +2751,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>172</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
+      </c>
+      <c r="C101" t="s">
+        <v>166</v>
       </c>
       <c r="D101" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -2605,13 +2765,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>174</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
+      </c>
+      <c r="C102" t="s">
+        <v>168</v>
       </c>
       <c r="D102" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -2619,13 +2779,13 @@
         <v>101</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -2633,13 +2793,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -2647,13 +2807,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C105" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D105" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -2661,13 +2821,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C106" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D106" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -2675,10 +2835,10 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C107" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -2686,10 +2846,10 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D108" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -2713,10 +2873,10 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C111" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -2724,10 +2884,10 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C112" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -2735,13 +2895,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C113" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D113" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -2749,13 +2909,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C114" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D114" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -2763,13 +2923,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C115" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D115" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -2777,13 +2937,13 @@
         <v>114</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D116" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -2791,13 +2951,13 @@
         <v>115</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -2805,13 +2965,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D118" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -2819,13 +2979,13 @@
         <v>117</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D119" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -2833,13 +2993,13 @@
         <v>118</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D120" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -2847,13 +3007,13 @@
         <v>119</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D121" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -2877,13 +3037,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C124" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D124" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -2891,13 +3051,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C125" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D125" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -2905,13 +3065,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C126" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D126" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -2919,13 +3079,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C127" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D127" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -2933,13 +3093,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C128" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D128" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -2947,13 +3107,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C129" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D129" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -2961,13 +3121,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C130" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D130" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -2975,13 +3135,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C131" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D131" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
@@ -3005,13 +3165,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C134" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D134" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -3019,13 +3179,13 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C135" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D135" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -3033,13 +3193,13 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C136" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D136" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -3047,13 +3207,13 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C137" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D137" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
@@ -3061,13 +3221,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C138" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D138" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -3075,13 +3235,13 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C139" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D139" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
@@ -3089,10 +3249,10 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C140" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
@@ -3100,13 +3260,13 @@
         <v>139</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D141" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -3114,13 +3274,13 @@
         <v>140</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D142" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -3128,13 +3288,13 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C143" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D143" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -3142,13 +3302,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C144" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D144" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -3156,10 +3316,10 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D145" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">

--- a/STM32F407ZGT6_PinMux.xlsx
+++ b/STM32F407ZGT6_PinMux.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yourfather\Desktop\stm32f407\github\20250606\study\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yourfather\Desktop\stm32f407\github\20250608\1\study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09F8F41B-3416-4EB0-85A3-8B6579177378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FEBB9E-0463-41F7-ABD4-3AC6B496B354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{E862E505-DAE5-417D-B231-6254909BD249}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="268">
   <si>
     <t>STM32F407ZGT6</t>
   </si>
@@ -99,21 +99,12 @@
     <t>PF0</t>
   </si>
   <si>
-    <t>FSMC_A0 / I2C2_SDA /EVENTOUT</t>
-  </si>
-  <si>
     <t>PF1</t>
   </si>
   <si>
-    <t>FSMC_A1 / I2C2_SCL /EVENTOUT</t>
-  </si>
-  <si>
     <t>PF2</t>
   </si>
   <si>
-    <t>FSMC_A2 / I2C2_SMBA /EVENTOUT</t>
-  </si>
-  <si>
     <t>PF3</t>
   </si>
   <si>
@@ -201,15 +192,9 @@
     <t>PC2</t>
   </si>
   <si>
-    <t>PC2 /SPI2_MISO /OTG_HS_ULPI_DIR /ETH_MII_TXD2/I2S2ext_SD/ EVENTOUT/ADC123_IN12</t>
-  </si>
-  <si>
     <t>PC3</t>
   </si>
   <si>
-    <t>PC3 /SPI2_MOSI / I2S2_SD /OTG_HS_ULPI_NXT /ETH_MII_TX_CLK/EVENTOUT/ADC123_IN13</t>
-  </si>
-  <si>
     <t>VSSA</t>
   </si>
   <si>
@@ -222,39 +207,21 @@
     <t>PA0</t>
   </si>
   <si>
-    <t>USART2_CTS/UART4_TX/ETH_MII_CRS /TIM2_CH1_ETR/TIM5_CH1 / TIM8_ETR/EVENTOUT/ADC123_IN0/WKUP(4)</t>
-  </si>
-  <si>
     <t>PA1</t>
   </si>
   <si>
-    <t>USART2_RTS /UART4_RX/ETH_RMII_REF_CLK /ETH_MII_RX_CLK /TIM5_CH2 / TIM2_CH2/EVENTOUT/ADC123_IN1</t>
-  </si>
-  <si>
     <t>PA2</t>
   </si>
   <si>
-    <t>USART2_TX/TIM5_CH3 /TIM9_CH1 / TIM2_CH3 /ETH_MDIO/ EVENTOUT/ADC123_IN2</t>
-  </si>
-  <si>
     <t>PA3</t>
   </si>
   <si>
-    <t>USART2_RX/TIM5_CH4 /TIM9_CH2 / TIM2_CH4 /OTG_HS_ULPI_D0 /ETH_MII_COL/EVENTOUT/ADC123_IN3</t>
-  </si>
-  <si>
     <t>PA4</t>
   </si>
   <si>
-    <t>SPI1_NSS / SPI3_NSS /USART2_CK /DCMI_HSYNC /OTG_HS_SOF/ I2S3_WS/EVENTOUT/ADC12_IN4/DAC_OUT1</t>
-  </si>
-  <si>
     <t>PA5</t>
   </si>
   <si>
-    <t>PA5/SPI1_SCK/OTG_HS_ULPI_CK /TIM2_CH1_ETR/TIM8_CH1N/ EVENTOUT/ADC12_IN5/DAC_OUT2</t>
-  </si>
-  <si>
     <t>PA6</t>
   </si>
   <si>
@@ -393,9 +360,6 @@
     <t>PB10</t>
   </si>
   <si>
-    <t>SPI2_SCK / I2S2_CK /I2C2_SCL/ USART3_TX /OTG_HS_ULPI_D3 /ETH_MII_RX_ER /TIM2_CH3/ EVENTOUT</t>
-  </si>
-  <si>
     <t>PB11</t>
   </si>
   <si>
@@ -411,9 +375,6 @@
     <t>PB12</t>
   </si>
   <si>
-    <t>SPI2_NSS / I2S2_WS /I2C2_SMBA/USART3_CK/ TIM1_BKIN /CAN2_RX /OTG_HS_ULPI_D5/ETH_RMII_TXD0 /ETH_MII_TXD0/OTG_HS_ID/ EVENTOUT</t>
-  </si>
-  <si>
     <t>PB13</t>
   </si>
   <si>
@@ -708,21 +669,12 @@
     <t>PB5</t>
   </si>
   <si>
-    <t>I2C1_SMBA/ CAN2_RX /OTG_HS_ULPI_D7 /ETH_PPS_OUT/TIM3_CH2/ SPI1_MOSI/ SPI3_MOSI /DCMI_D10 / I2S3_SD/EVENTOUT</t>
-  </si>
-  <si>
     <t>PB6</t>
   </si>
   <si>
-    <t>I2C1_SCL/ TIM4_CH1 /CAN2_TX /DCMI_D5/USART1_TX/EVENTOUT</t>
-  </si>
-  <si>
     <t>PB7</t>
   </si>
   <si>
-    <t>I2C1_SDA / FSMC_NL /DCMI_VSYNC /USART1_RX/ TIM4_CH2/EVENTOUT</t>
-  </si>
-  <si>
     <t>BOOT0</t>
   </si>
   <si>
@@ -733,9 +685,6 @@
   </si>
   <si>
     <t>PB9</t>
-  </si>
-  <si>
-    <t>SPI2_NSS/ I2S2_WS /TIM4_CH4/ TIM11_CH1/SDIO_D5 / DCMI_D7 /I2C1_SDA / CAN1_TX/EVENTOUT</t>
   </si>
   <si>
     <t>PE0</t>
@@ -1030,6 +979,382 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> /TIM14_CH1/TIM3_CH2/ETH_MII_RX_DV /TIM1_CH1N /ETH_RMII_CRS_DV/EVENTOUT/ADC12_IN7</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>PC2 /</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPI2_MISO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> /OTG_HS_ULPI_DIR /ETH_MII_TXD2/I2S2ext_SD/ EVENTOUT/ADC123_IN12</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>PC3 /</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPI2_MOSI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / I2S2_SD /OTG_HS_ULPI_NXT /ETH_MII_TX_CLK/EVENTOUT/ADC123_IN13</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SPI2_SCK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ I2S2_CK /I2C2_SCL/ USART3_TX /OTG_HS_ULPI_D3 /ETH_MII_RX_ER /TIM2_CH3/ EVENTOUT</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPI2_NSS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / I2S2_WS /I2C2_SMBA/USART3_CK/ TIM1_BKIN /CAN2_RX /OTG_HS_ULPI_D5/ETH_RMII_TXD0 /ETH_MII_TXD0/OTG_HS_ID/ EVENTOUT</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPI2_NSS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ I2S2_WS /TIM4_CH4/ TIM11_CH1/SDIO_D5 / DCMI_D7 /I2C1_SDA / CAN1_TX/EVENTOUT</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I2C1_SMBA/ CAN2_RX /OTG_HS_ULPI_D7 /ETH_PPS_OUT/TIM3_CH2/ SPI1_MOSI/ SPI3_MOSI /DCMI_D10 / I2S3_SD/EVENTOUT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>FSMC_A0 /</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> I2C2_SDA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> /EVENTOUT</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FSMC_A2 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I2C2_SMBA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> /EVENTOUT</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>USART2_TX/TIM5_CH3 /TIM9_CH1 / TIM2_CH3 /ETH_MDIO/ EVENTOUT/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ADC123_IN2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>USART2_RX/TIM5_CH4 /TIM9_CH2 / TIM2_CH4 /OTG_HS_ULPI_D0 /ETH_MII_COL/EVENTOUT/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ADC123_IN3</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>USART2_RTS /UART4_RX/ETH_RMII_REF_CLK /ETH_MII_RX_CLK /TIM5_CH2 / TIM2_CH2/EVENTOUT/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ADC123_IN1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>USART2_CTS/UART4_TX/ETH_MII_CRS /TIM2_CH1_ETR/TIM5_CH1 / TIM8_ETR/EVENTOUT/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ADC123_IN0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/WKUP(4)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SPI1_NSS / SPI3_NSS /USART2_CK /DCMI_HSYNC /OTG_HS_SOF/ I2S3_WS/EVENTOUT/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ADC12_IN4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/DAC_OUT1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>PA5/SPI1_SCK/OTG_HS_ULPI_CK /TIM2_CH1_ETR/TIM8_CH1N/ EVENTOUT/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ADC12_IN5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/DAC_OUT2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I2C1_SCL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ TIM4_CH1 /CAN2_TX /DCMI_D5/USART1_TX/EVENTOUT</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I2C1_SDA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / FSMC_NL /DCMI_VSYNC /USART1_RX/ TIM4_CH2/EVENTOUT</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1616,7 +1941,7 @@
         <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1624,13 +1949,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1638,13 +1960,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1652,13 +1974,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1666,13 +1988,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1680,13 +2002,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1694,10 +2016,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1705,10 +2027,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1716,13 +2038,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1730,13 +2052,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1744,13 +2066,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1758,13 +2080,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1772,13 +2094,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1786,13 +2108,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1800,13 +2122,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1814,10 +2136,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1825,13 +2147,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1839,13 +2161,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1853,13 +2175,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1867,13 +2189,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>60</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1881,7 +2203,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1889,7 +2211,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1897,7 +2219,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1905,7 +2227,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1913,13 +2235,13 @@
         <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="D36" t="s">
-        <v>65</v>
+        <v>263</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1927,13 +2249,13 @@
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D37" t="s">
-        <v>67</v>
+        <v>262</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1941,13 +2263,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="D38" t="s">
-        <v>69</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1955,13 +2277,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="D39" t="s">
-        <v>71</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1969,7 +2291,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1977,7 +2299,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1985,13 +2307,13 @@
         <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C42" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="D42" t="s">
-        <v>73</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1999,13 +2321,13 @@
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="D43" t="s">
-        <v>75</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2013,13 +2335,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C44" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D44" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2027,13 +2349,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2041,13 +2363,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C46" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D46" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2055,13 +2377,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D47" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2069,13 +2391,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C48" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D48" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2083,13 +2405,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C49" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2097,10 +2419,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2108,13 +2430,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C51" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D51" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2122,13 +2444,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C52" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D52" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2136,7 +2458,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2144,7 +2466,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -2152,13 +2474,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C55" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D55" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -2166,13 +2488,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C56" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D56" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2180,13 +2502,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C57" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D57" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -2194,13 +2516,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C58" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D58" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -2208,13 +2530,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C59" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D59" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2222,13 +2544,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D60" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -2236,13 +2558,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C61" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D61" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -2250,13 +2572,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C62" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2264,7 +2586,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -2272,7 +2594,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -2280,13 +2602,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C65" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D65" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -2294,13 +2616,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C66" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D66" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -2308,13 +2630,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C67" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D67" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -2322,13 +2644,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C68" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D68" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -2336,13 +2658,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C69" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D69" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2350,13 +2672,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C70" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D70" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -2364,13 +2686,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
-      </c>
-      <c r="D71" t="s">
-        <v>122</v>
+        <v>110</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -2378,13 +2700,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C72" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D72" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -2392,10 +2714,10 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D73" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -2403,7 +2725,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -2411,13 +2733,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C75" t="s">
-        <v>127</v>
-      </c>
-      <c r="D75" t="s">
-        <v>128</v>
+        <v>115</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -2425,13 +2747,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C76" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D76" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -2439,13 +2761,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D77" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -2453,13 +2775,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D78" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -2467,13 +2789,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C79" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="D79" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -2481,13 +2803,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="C80" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D80" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -2495,13 +2817,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C81" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="D81" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2509,13 +2831,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C82" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="D82" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -2523,13 +2845,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C83" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="D83" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -2537,13 +2859,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="C84" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D84" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -2551,7 +2873,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -2559,7 +2881,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -2567,13 +2889,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="C87" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D87" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -2581,13 +2903,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C88" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="D88" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -2595,13 +2917,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="C89" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="D89" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -2609,13 +2931,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="C90" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="D90" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -2623,13 +2945,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="C91" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="D91" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -2637,13 +2959,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C92" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="D92" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -2651,13 +2973,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="C93" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D93" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -2665,13 +2987,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="C94" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="D94" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -2679,13 +3001,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C95" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="D95" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -2693,7 +3015,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -2701,7 +3023,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -2709,13 +3031,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D98" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -2723,13 +3045,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D99" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -2737,13 +3059,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -2751,13 +3073,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C101" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="D101" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -2765,13 +3087,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="C102" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D102" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -2779,13 +3101,13 @@
         <v>101</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -2793,13 +3115,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -2807,13 +3129,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="C105" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="D105" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -2821,13 +3143,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="C106" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D106" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -2835,10 +3157,10 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C107" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -2846,10 +3168,10 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D108" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -2857,7 +3179,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -2865,7 +3187,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -2873,10 +3195,10 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C111" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -2884,10 +3206,10 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="C112" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -2895,13 +3217,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C113" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D113" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -2909,13 +3231,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="C114" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="D114" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -2923,13 +3245,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C115" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D115" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -2937,13 +3259,13 @@
         <v>114</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="D116" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -2951,13 +3273,13 @@
         <v>115</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D117" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -2965,13 +3287,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="D118" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -2979,13 +3301,13 @@
         <v>117</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="D119" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -2993,13 +3315,13 @@
         <v>118</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="D120" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -3007,13 +3329,13 @@
         <v>119</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="D121" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -3021,7 +3343,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -3029,7 +3351,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -3037,13 +3359,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C124" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D124" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -3051,13 +3373,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="C125" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="D125" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -3065,13 +3387,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C126" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="D126" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -3079,13 +3401,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="C127" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="D127" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -3093,13 +3415,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="C128" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="D128" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -3107,13 +3429,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="C129" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="D129" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -3121,13 +3443,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C130" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="D130" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -3135,13 +3457,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C131" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="D131" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
@@ -3149,7 +3471,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -3157,7 +3479,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
@@ -3165,13 +3487,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="C134" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D134" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -3179,13 +3501,13 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C135" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="D135" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -3193,13 +3515,13 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C136" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D136" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -3207,13 +3529,13 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C137" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="D137" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
@@ -3221,13 +3543,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C138" t="s">
-        <v>228</v>
-      </c>
-      <c r="D138" t="s">
-        <v>229</v>
+        <v>214</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -3235,13 +3557,13 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C139" t="s">
-        <v>230</v>
-      </c>
-      <c r="D139" t="s">
-        <v>231</v>
+        <v>215</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
@@ -3249,10 +3571,10 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="C140" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
@@ -3260,13 +3582,13 @@
         <v>139</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="D141" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -3274,13 +3596,13 @@
         <v>140</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D142" t="s">
-        <v>236</v>
+        <v>233</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -3288,13 +3610,13 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="C143" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="D143" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -3302,13 +3624,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="C144" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="D144" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -3316,10 +3638,10 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="D145" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -3327,7 +3649,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/STM32F407ZGT6_PinMux.xlsx
+++ b/STM32F407ZGT6_PinMux.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yourfather\Desktop\stm32f407\github\20250608\1\study\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yourfather\Desktop\stm32f407\github\20250609\study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FEBB9E-0463-41F7-ABD4-3AC6B496B354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE85B4C-130B-4BE2-9285-92545B836BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{E862E505-DAE5-417D-B231-6254909BD249}"/>
   </bookViews>
@@ -378,9 +378,6 @@
     <t>PB13</t>
   </si>
   <si>
-    <t>SPI2_SCK / I2S2_CK /USART3_CTS/TIM1_CH1N /CAN2_TX /OTG_HS_ULPI_D6 /ETH_RMII_TXD1 /ETH_MII_TXD1/EVENTOUT/OTG_HS_VBUS</t>
-  </si>
-  <si>
     <t>PB14</t>
   </si>
   <si>
@@ -1048,7 +1045,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SPI2_SCK </t>
+      <t>SPI2_NSS</t>
     </r>
     <r>
       <rPr>
@@ -1059,57 +1056,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>/ I2S2_CK /I2C2_SCL/ USART3_TX /OTG_HS_ULPI_D3 /ETH_MII_RX_ER /TIM2_CH3/ EVENTOUT</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SPI2_NSS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> / I2S2_WS /I2C2_SMBA/USART3_CK/ TIM1_BKIN /CAN2_RX /OTG_HS_ULPI_D5/ETH_RMII_TXD0 /ETH_MII_TXD0/OTG_HS_ID/ EVENTOUT</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SPI2_NSS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/ I2S2_WS /TIM4_CH4/ TIM11_CH1/SDIO_D5 / DCMI_D7 /I2C1_SDA / CAN1_TX/EVENTOUT</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1355,6 +1302,79 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> / FSMC_NL /DCMI_VSYNC /USART1_RX/ TIM4_CH2/EVENTOUT</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SPI2_SCK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ I2S2_CK /I2C2_SCL/ USART3_TX /OTG_HS_ULPI_D3 /ETH_MII_RX_ER /TIM2_CH3/ EVENTOUT</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SPI2_SCK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ I2S2_CK /USART3_CTS/TIM1_CH1N /CAN2_TX /OTG_HS_ULPI_D6 /ETH_RMII_TXD1 /ETH_MII_TXD1/EVENTOUT/OTG_HS_VBUS</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPI2_NSS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ I2S2_WS /TIM4_CH4/ TIM11_CH1/SDIO_D5 / DCMI_D7 /I2C1_SDA / CAN1_TX/EVENTOUT</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1941,7 +1961,7 @@
         <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1966,7 +1986,7 @@
         <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2083,7 +2103,7 @@
         <v>40</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D23" t="s">
         <v>41</v>
@@ -2097,7 +2117,7 @@
         <v>42</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D24" t="s">
         <v>43</v>
@@ -2181,7 +2201,7 @@
         <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2195,7 +2215,7 @@
         <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2238,10 +2258,10 @@
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D36" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,10 +2272,10 @@
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2266,10 +2286,10 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D38" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2280,10 +2300,10 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D39" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2310,10 +2330,10 @@
         <v>63</v>
       </c>
       <c r="C42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D42" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2324,10 +2344,10 @@
         <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D43" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2355,7 +2375,7 @@
         <v>67</v>
       </c>
       <c r="D45" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2692,7 +2712,7 @@
         <v>110</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -2739,7 +2759,7 @@
         <v>115</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -2752,8 +2772,8 @@
       <c r="C76" t="s">
         <v>116</v>
       </c>
-      <c r="D76" t="s">
-        <v>117</v>
+      <c r="D76" s="2" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -2761,13 +2781,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D77" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -2775,13 +2795,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D78" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -2789,13 +2809,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
+        <v>119</v>
+      </c>
+      <c r="C79" t="s">
+        <v>119</v>
+      </c>
+      <c r="D79" t="s">
         <v>120</v>
-      </c>
-      <c r="C79" t="s">
-        <v>120</v>
-      </c>
-      <c r="D79" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -2803,13 +2823,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
+        <v>121</v>
+      </c>
+      <c r="C80" t="s">
+        <v>121</v>
+      </c>
+      <c r="D80" t="s">
         <v>122</v>
-      </c>
-      <c r="C80" t="s">
-        <v>122</v>
-      </c>
-      <c r="D80" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -2817,13 +2837,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
+        <v>123</v>
+      </c>
+      <c r="C81" t="s">
+        <v>123</v>
+      </c>
+      <c r="D81" t="s">
         <v>124</v>
-      </c>
-      <c r="C81" t="s">
-        <v>124</v>
-      </c>
-      <c r="D81" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2831,13 +2851,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
+        <v>125</v>
+      </c>
+      <c r="C82" t="s">
+        <v>125</v>
+      </c>
+      <c r="D82" t="s">
         <v>126</v>
-      </c>
-      <c r="C82" t="s">
-        <v>126</v>
-      </c>
-      <c r="D82" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -2845,13 +2865,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
+        <v>127</v>
+      </c>
+      <c r="C83" t="s">
+        <v>127</v>
+      </c>
+      <c r="D83" t="s">
         <v>128</v>
-      </c>
-      <c r="C83" t="s">
-        <v>128</v>
-      </c>
-      <c r="D83" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -2859,13 +2879,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
+        <v>129</v>
+      </c>
+      <c r="C84" t="s">
+        <v>129</v>
+      </c>
+      <c r="D84" t="s">
         <v>130</v>
-      </c>
-      <c r="C84" t="s">
-        <v>130</v>
-      </c>
-      <c r="D84" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -2889,13 +2909,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
+        <v>131</v>
+      </c>
+      <c r="C87" t="s">
+        <v>131</v>
+      </c>
+      <c r="D87" t="s">
         <v>132</v>
-      </c>
-      <c r="C87" t="s">
-        <v>132</v>
-      </c>
-      <c r="D87" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -2903,13 +2923,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
+        <v>133</v>
+      </c>
+      <c r="C88" t="s">
+        <v>133</v>
+      </c>
+      <c r="D88" t="s">
         <v>134</v>
-      </c>
-      <c r="C88" t="s">
-        <v>134</v>
-      </c>
-      <c r="D88" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -2917,13 +2937,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
+        <v>135</v>
+      </c>
+      <c r="C89" t="s">
+        <v>135</v>
+      </c>
+      <c r="D89" t="s">
         <v>136</v>
-      </c>
-      <c r="C89" t="s">
-        <v>136</v>
-      </c>
-      <c r="D89" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -2931,13 +2951,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
+        <v>137</v>
+      </c>
+      <c r="C90" t="s">
+        <v>137</v>
+      </c>
+      <c r="D90" t="s">
         <v>138</v>
-      </c>
-      <c r="C90" t="s">
-        <v>138</v>
-      </c>
-      <c r="D90" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -2945,13 +2965,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
+        <v>139</v>
+      </c>
+      <c r="C91" t="s">
+        <v>139</v>
+      </c>
+      <c r="D91" t="s">
         <v>140</v>
-      </c>
-      <c r="C91" t="s">
-        <v>140</v>
-      </c>
-      <c r="D91" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -2959,13 +2979,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
+        <v>141</v>
+      </c>
+      <c r="C92" t="s">
+        <v>141</v>
+      </c>
+      <c r="D92" t="s">
         <v>142</v>
-      </c>
-      <c r="C92" t="s">
-        <v>142</v>
-      </c>
-      <c r="D92" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -2973,13 +2993,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
+        <v>143</v>
+      </c>
+      <c r="C93" t="s">
+        <v>143</v>
+      </c>
+      <c r="D93" t="s">
         <v>144</v>
-      </c>
-      <c r="C93" t="s">
-        <v>144</v>
-      </c>
-      <c r="D93" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -2987,13 +3007,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
+        <v>145</v>
+      </c>
+      <c r="C94" t="s">
+        <v>145</v>
+      </c>
+      <c r="D94" t="s">
         <v>146</v>
-      </c>
-      <c r="C94" t="s">
-        <v>146</v>
-      </c>
-      <c r="D94" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -3001,13 +3021,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
+        <v>147</v>
+      </c>
+      <c r="C95" t="s">
+        <v>147</v>
+      </c>
+      <c r="D95" t="s">
         <v>148</v>
-      </c>
-      <c r="C95" t="s">
-        <v>148</v>
-      </c>
-      <c r="D95" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -3031,13 +3051,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D98" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -3045,13 +3065,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D99" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -3059,13 +3079,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -3073,13 +3093,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
+        <v>152</v>
+      </c>
+      <c r="C101" t="s">
+        <v>152</v>
+      </c>
+      <c r="D101" t="s">
         <v>153</v>
-      </c>
-      <c r="C101" t="s">
-        <v>153</v>
-      </c>
-      <c r="D101" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -3087,13 +3107,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
+        <v>154</v>
+      </c>
+      <c r="C102" t="s">
+        <v>154</v>
+      </c>
+      <c r="D102" t="s">
         <v>155</v>
-      </c>
-      <c r="C102" t="s">
-        <v>155</v>
-      </c>
-      <c r="D102" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -3101,13 +3121,13 @@
         <v>101</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -3115,13 +3135,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -3129,13 +3149,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
+        <v>158</v>
+      </c>
+      <c r="C105" t="s">
+        <v>158</v>
+      </c>
+      <c r="D105" t="s">
         <v>159</v>
-      </c>
-      <c r="C105" t="s">
-        <v>159</v>
-      </c>
-      <c r="D105" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -3143,13 +3163,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
+        <v>160</v>
+      </c>
+      <c r="C106" t="s">
+        <v>160</v>
+      </c>
+      <c r="D106" t="s">
         <v>161</v>
-      </c>
-      <c r="C106" t="s">
-        <v>161</v>
-      </c>
-      <c r="D106" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -3157,10 +3177,10 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
+        <v>162</v>
+      </c>
+      <c r="C107" t="s">
         <v>163</v>
-      </c>
-      <c r="C107" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -3168,10 +3188,10 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
+        <v>164</v>
+      </c>
+      <c r="D108" t="s">
         <v>165</v>
-      </c>
-      <c r="D108" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -3195,10 +3215,10 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
+        <v>166</v>
+      </c>
+      <c r="C111" t="s">
         <v>167</v>
-      </c>
-      <c r="C111" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -3206,10 +3226,10 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
+        <v>168</v>
+      </c>
+      <c r="C112" t="s">
         <v>169</v>
-      </c>
-      <c r="C112" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -3217,13 +3237,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
+        <v>170</v>
+      </c>
+      <c r="C113" t="s">
+        <v>170</v>
+      </c>
+      <c r="D113" t="s">
         <v>171</v>
-      </c>
-      <c r="C113" t="s">
-        <v>171</v>
-      </c>
-      <c r="D113" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -3231,13 +3251,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
+        <v>172</v>
+      </c>
+      <c r="C114" t="s">
+        <v>172</v>
+      </c>
+      <c r="D114" t="s">
         <v>173</v>
-      </c>
-      <c r="C114" t="s">
-        <v>173</v>
-      </c>
-      <c r="D114" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -3245,13 +3265,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
+        <v>174</v>
+      </c>
+      <c r="C115" t="s">
+        <v>174</v>
+      </c>
+      <c r="D115" t="s">
         <v>175</v>
-      </c>
-      <c r="C115" t="s">
-        <v>175</v>
-      </c>
-      <c r="D115" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -3259,13 +3279,13 @@
         <v>114</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D116" t="s">
         <v>177</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D116" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -3273,13 +3293,13 @@
         <v>115</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D117" t="s">
         <v>179</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D117" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -3287,13 +3307,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D118" t="s">
         <v>181</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D118" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -3301,13 +3321,13 @@
         <v>117</v>
       </c>
       <c r="B119" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D119" t="s">
         <v>183</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D119" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -3315,13 +3335,13 @@
         <v>118</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D120" t="s">
         <v>185</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D120" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -3329,13 +3349,13 @@
         <v>119</v>
       </c>
       <c r="B121" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D121" t="s">
         <v>187</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D121" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -3359,13 +3379,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
+        <v>188</v>
+      </c>
+      <c r="C124" t="s">
+        <v>188</v>
+      </c>
+      <c r="D124" t="s">
         <v>189</v>
-      </c>
-      <c r="C124" t="s">
-        <v>189</v>
-      </c>
-      <c r="D124" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -3373,13 +3393,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
+        <v>190</v>
+      </c>
+      <c r="C125" t="s">
+        <v>190</v>
+      </c>
+      <c r="D125" t="s">
         <v>191</v>
-      </c>
-      <c r="C125" t="s">
-        <v>191</v>
-      </c>
-      <c r="D125" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -3387,13 +3407,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
+        <v>192</v>
+      </c>
+      <c r="C126" t="s">
+        <v>192</v>
+      </c>
+      <c r="D126" t="s">
         <v>193</v>
-      </c>
-      <c r="C126" t="s">
-        <v>193</v>
-      </c>
-      <c r="D126" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -3401,13 +3421,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
+        <v>194</v>
+      </c>
+      <c r="C127" t="s">
+        <v>194</v>
+      </c>
+      <c r="D127" t="s">
         <v>195</v>
-      </c>
-      <c r="C127" t="s">
-        <v>195</v>
-      </c>
-      <c r="D127" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -3415,13 +3435,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
+        <v>196</v>
+      </c>
+      <c r="C128" t="s">
+        <v>196</v>
+      </c>
+      <c r="D128" t="s">
         <v>197</v>
-      </c>
-      <c r="C128" t="s">
-        <v>197</v>
-      </c>
-      <c r="D128" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -3429,13 +3449,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
+        <v>198</v>
+      </c>
+      <c r="C129" t="s">
+        <v>198</v>
+      </c>
+      <c r="D129" t="s">
         <v>199</v>
-      </c>
-      <c r="C129" t="s">
-        <v>199</v>
-      </c>
-      <c r="D129" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -3443,13 +3463,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
+        <v>200</v>
+      </c>
+      <c r="C130" t="s">
+        <v>200</v>
+      </c>
+      <c r="D130" t="s">
         <v>201</v>
-      </c>
-      <c r="C130" t="s">
-        <v>201</v>
-      </c>
-      <c r="D130" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -3457,13 +3477,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
+        <v>202</v>
+      </c>
+      <c r="C131" t="s">
+        <v>202</v>
+      </c>
+      <c r="D131" t="s">
         <v>203</v>
-      </c>
-      <c r="C131" t="s">
-        <v>203</v>
-      </c>
-      <c r="D131" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
@@ -3487,13 +3507,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
+        <v>204</v>
+      </c>
+      <c r="C134" t="s">
+        <v>204</v>
+      </c>
+      <c r="D134" t="s">
         <v>205</v>
-      </c>
-      <c r="C134" t="s">
-        <v>205</v>
-      </c>
-      <c r="D134" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -3501,13 +3521,13 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
+        <v>206</v>
+      </c>
+      <c r="C135" t="s">
         <v>207</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
         <v>208</v>
-      </c>
-      <c r="D135" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -3515,13 +3535,13 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
+        <v>209</v>
+      </c>
+      <c r="C136" t="s">
         <v>210</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
         <v>211</v>
-      </c>
-      <c r="D136" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -3529,13 +3549,13 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C137" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D137" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
@@ -3543,13 +3563,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C138" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -3557,13 +3577,13 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C139" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
@@ -3571,10 +3591,10 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C140" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
@@ -3582,13 +3602,13 @@
         <v>139</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D141" t="s">
         <v>217</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D141" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -3596,13 +3616,13 @@
         <v>140</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -3610,13 +3630,13 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
+        <v>219</v>
+      </c>
+      <c r="C143" t="s">
+        <v>219</v>
+      </c>
+      <c r="D143" t="s">
         <v>220</v>
-      </c>
-      <c r="C143" t="s">
-        <v>220</v>
-      </c>
-      <c r="D143" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -3624,13 +3644,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
+        <v>221</v>
+      </c>
+      <c r="C144" t="s">
+        <v>221</v>
+      </c>
+      <c r="D144" t="s">
         <v>222</v>
-      </c>
-      <c r="C144" t="s">
-        <v>222</v>
-      </c>
-      <c r="D144" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -3638,10 +3658,10 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
+        <v>223</v>
+      </c>
+      <c r="D145" t="s">
         <v>224</v>
-      </c>
-      <c r="D145" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
